--- a/Tables/Data/GameAttrInitTable.xlsx
+++ b/Tables/Data/GameAttrInitTable.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\__Dev\GAIS\Tables\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__Dev\GAIS\Tables\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -49,7 +49,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>(map#sep=:|),battle.EGameAttr,float</t>
+    <t>map,battle.EGameAttr,float</t>
   </si>
   <si>
     <t>##</t>
@@ -58,10 +58,52 @@
     <t>备注</t>
   </si>
   <si>
-    <t>刺客老鹰</t>
-  </si>
-  <si>
-    <t>最大血量Base:100|最大血量Mult:1|攻击力Base:50|攻击力Mult:0.2</t>
+    <t>主角</t>
+  </si>
+  <si>
+    <t>最大血量Base</t>
+  </si>
+  <si>
+    <t>攻击力Base</t>
+  </si>
+  <si>
+    <t>暴击率Base</t>
+  </si>
+  <si>
+    <t>暴击倍率Base</t>
+  </si>
+  <si>
+    <t>行动充能Base</t>
+  </si>
+  <si>
+    <t>第1关</t>
+  </si>
+  <si>
+    <t>第2关</t>
+  </si>
+  <si>
+    <t>第3关</t>
+  </si>
+  <si>
+    <t>第4关</t>
+  </si>
+  <si>
+    <t>第5关 BOOS</t>
+  </si>
+  <si>
+    <t>第6关</t>
+  </si>
+  <si>
+    <t>第7关</t>
+  </si>
+  <si>
+    <t>第8关</t>
+  </si>
+  <si>
+    <t>第9关</t>
+  </si>
+  <si>
+    <t>第10关 BOSS</t>
   </si>
 </sst>
 </file>
@@ -434,7 +476,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -462,6 +504,30 @@
         <color auto="1"/>
       </left>
       <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -594,7 +660,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -606,34 +672,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -718,7 +784,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -731,7 +797,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1267,18 +1339,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="7.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="62.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="7.37272727272727" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.87272727272727" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.2545454545455" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.6363636363636" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.45454545454545" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.8181818181818" style="2" customWidth="1"/>
+    <col min="7" max="7" width="5.27272727272727" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.3636363636364" style="2" customWidth="1"/>
+    <col min="9" max="10" width="14.6363636363636" style="2" customWidth="1"/>
+    <col min="11" max="11" width="5.27272727272727" style="2" customWidth="1"/>
+    <col min="12" max="12" width="20.2727272727273" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" customHeight="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" ht="15" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1289,8 +1367,17 @@
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="6"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:4">
+    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1301,8 +1388,17 @@
       <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="6"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" customHeight="1" spans="1:4">
+    <row r="3" s="1" customFormat="1" ht="15" customHeight="1" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1310,8 +1406,17 @@
         <v>7</v>
       </c>
       <c r="D3" s="4"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="6"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:13">
       <c r="B4" s="2">
         <v>1001</v>
       </c>
@@ -1321,8 +1426,436 @@
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="E4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2">
+        <v>100</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6" s="2">
+        <v>2002</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" ref="E6:E13" si="0">E5+500</f>
+        <v>1500</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" ref="G5:G13" si="1">G5+10</f>
+        <v>110</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="B7" s="2">
+        <v>2003</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="2">
+        <v>2004</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="B9" s="2">
+        <v>2005</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2">
+        <f>E8*2</f>
+        <v>5000</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2">
+        <f>G8*2</f>
+        <v>260</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="2">
+        <v>3</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="2">
+        <v>2006</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3000</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2">
+        <v>140</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="B11" s="2">
+        <v>2007</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="B12" s="2">
+        <v>2008</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="B13" s="2">
+        <v>2009</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="B14" s="2">
+        <v>2010</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2">
+        <f>E13*2</f>
+        <v>9000</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2">
+        <f>G13*2</f>
+        <v>340</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="2">
+        <v>3</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.25</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D1:M1"/>
+    <mergeCell ref="D2:M2"/>
+    <mergeCell ref="D3:M3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
